--- a/exports/32840_paquichari.xlsx
+++ b/exports/32840_paquichari.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M182"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,22 +738,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>91808823</t>
+          <t>91773557</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AIQUIPA</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PAQUIYAURI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ALEXIA ANGHELINA</t>
+          <t>JHOSELIN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>09/04/2020</t>
+          <t>13/03/2020</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>13/03/2025</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -801,22 +801,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23382349</t>
+          <t>45466806</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ALANYA</t>
+          <t>ALMONACID</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARAUJO</t>
+          <t>QUINTO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SANTA TEREZA MARUJA</t>
+          <t>NOELIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>15/10/1970</t>
+          <t>20/01/1988</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>20/03/2015</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -864,27 +864,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>91773557</t>
+          <t>91703633</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>ALTAMIRANO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PAQUIYAURI</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JHOSELIN</t>
+          <t>RUSSER EMIR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13/03/2020</t>
+          <t>29/01/2020</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13/03/2025</t>
+          <t>29/01/2025</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -927,22 +927,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>45466806</t>
+          <t>91983316</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALMONACID</t>
+          <t>ANYOSA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>QUINTO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NOELIA</t>
+          <t>RUTH INES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20/01/1988</t>
+          <t>23/08/2020</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20/03/2015</t>
+          <t>23/08/2025</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -990,22 +990,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>91703633</t>
+          <t>74174339</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALTAMIRANO</t>
+          <t>ARAUJO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RUSSER EMIR</t>
+          <t>RINZON</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29/01/2020</t>
+          <t>22/06/1996</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>29/01/2025</t>
+          <t>06/03/2024</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1053,27 +1053,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>91983316</t>
+          <t>92318026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ANYOSA</t>
+          <t>ARMAS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RUTH INES</t>
+          <t>NELSON VALENTINO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>23/08/2020</t>
+          <t>15/12/2020</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>23/08/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1116,22 +1116,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>74174339</t>
+          <t>81952183</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARAUJO</t>
+          <t>ATAO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RINZON</t>
+          <t>JULIO JHAFDET</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22/06/1996</t>
+          <t>09/05/2020</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>06/03/2024</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1179,45 +1179,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>92318026</t>
+          <t>42650507</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ARMAS</t>
+          <t>ATAO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NELSON VALENTINO</t>
+          <t>JOHANA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15/12/2020</t>
+          <t>19/10/1983</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1242,22 +1242,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>81952183</t>
+          <t>81767918</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATAO</t>
+          <t>AUQUI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JULIO JHAFDET</t>
+          <t>ISAK ISMAEL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>09/05/2020</t>
+          <t>13/04/2021</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1305,35 +1305,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>42650507</t>
+          <t>77708148</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATAO</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>CORPUS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JOHANA</t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19/10/1983</t>
+          <t>11/09/1996</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1368,22 +1368,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>81767918</t>
+          <t>92245541</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AUQUI</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ISAK ISMAEL</t>
+          <t>AARON JHOAN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13/04/2021</t>
+          <t>24/02/2021</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,7 +1431,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>77708148</t>
+          <t>43827868</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CORPUS</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t>ORLANDO PAUL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1455,11 +1455,11 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11/09/1996</t>
+          <t>08/04/1980</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1494,35 +1494,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>92245541</t>
+          <t>94165960</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>BARRA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CCORIMANYA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AARON JHOAN</t>
+          <t>BRIYITH XIMENA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24/02/2021</t>
+          <t>07/03/2025</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1557,22 +1557,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>43827868</t>
+          <t>81952189</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>BASTIDAS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ORLANDO PAUL</t>
+          <t>WILDER YANDEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>08/04/1980</t>
+          <t>24/10/2020</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1620,27 +1620,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>94165960</t>
+          <t>94416220</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BARRA</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CCORIMANYA</t>
+          <t>OCHANTE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BRIYITH XIMENA</t>
+          <t>CALEB GABRIEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>23/12/2025</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1683,27 +1683,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>81952189</t>
+          <t>91731887</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BASTIDAS</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>HUARCAYA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>WILDER YANDEL</t>
+          <t>LUHANA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>24/10/2020</t>
+          <t>16/02/2020</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>16/02/2025</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1746,22 +1746,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>94416220</t>
+          <t>40828403</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>BONIFACIO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OCHANTE</t>
+          <t>HIDALGO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CALEB GABRIEL</t>
+          <t>JOSE ANTONIO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>05/11/1979</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23/12/2025</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1809,35 +1809,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>91731887</t>
+          <t>92440477</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>CABALLERO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HUARCAYA</t>
+          <t>PILLACA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LUHANA</t>
+          <t>DIEGO LEONEL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>16/02/2020</t>
+          <t>08/07/2021</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>16/02/2025</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1872,22 +1872,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>40828403</t>
+          <t>48573984</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BONIFACIO</t>
+          <t>CANTORIN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>USCAMAYTA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO</t>
+          <t>LEANDRO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,11 +1896,11 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/11/1979</t>
+          <t>02/05/1989</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1935,35 +1935,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>92440477</t>
+          <t>94012660</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CABALLERO</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PILLACA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DIEGO LEONEL</t>
+          <t>KAORI AITANA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>08/07/2021</t>
+          <t>18/10/2024</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,22 +1998,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>48573984</t>
+          <t>72489411</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CANTORIN</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USCAMAYTA</t>
+          <t>CUSICHE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LEANDRO</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>02/05/1989</t>
+          <t>17/12/1994</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,22 +2061,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>94012660</t>
+          <t>94245502</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>LANDEO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KAORI AITANA</t>
+          <t>ELIANA AYELET</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2085,11 +2085,11 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>18/10/2024</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>72489411</t>
+          <t>81952238</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CUSICHE</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>JARRY JAESON</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>17/12/1994</t>
+          <t>09/09/2021</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>94245502</t>
+          <t>81952206</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2197,25 +2197,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LANDEO</t>
+          <t>YARANGA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ELIANA AYELET</t>
+          <t>BEK MAYKER</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>14/08/2020</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,27 +2250,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>81952206</t>
+          <t>91817312</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CARRASCO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YARANGA</t>
+          <t>ALCCA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BEK MAYKER</t>
+          <t>RUTH KIA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14/08/2020</t>
+          <t>16/04/2020</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14/08/2025</t>
+          <t>16/04/2025</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,22 +2313,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>91817312</t>
+          <t>92424584</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CARRASCO</t>
+          <t>CASAFRANCA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ALCCA</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RUTH KIA</t>
+          <t>MAYA YESHLEN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>16/04/2020</t>
+          <t>28/06/2021</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16/04/2025</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,22 +2376,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>92424584</t>
+          <t>91690354</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CASAFRANCA</t>
+          <t>CASAS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MAYA YESHLEN</t>
+          <t>SUSAN MARIA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,11 +2400,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>28/06/2021</t>
+          <t>20/01/2020</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>28/06/2026</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,22 +2439,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>91690354</t>
+          <t>90422154</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CASAS</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>UNCHUPAICO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SUSAN MARIA</t>
+          <t>KATALINA ISABELA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2463,11 +2463,11 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20/01/2020</t>
+          <t>22/09/2017</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,22 +2502,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>90422154</t>
+          <t>92158269</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNCHUPAICO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KATALINA ISABELA</t>
+          <t>LUCIANA DEYANIRA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2526,11 +2526,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22/09/2017</t>
+          <t>10/11/2020</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>92158269</t>
+          <t>92100040</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CARPIO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LUCIANA DEYANIRA</t>
+          <t>YOR DYLAN SAID</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10/11/2020</t>
+          <t>08/11/2020</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,7 +2628,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>92100040</t>
+          <t>94464693</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CARPIO</t>
+          <t>POMARI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>YOR DYLAN SAID</t>
+          <t>DILAN ELIAS</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2652,11 +2652,11 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>08/11/2020</t>
+          <t>30/11/2025</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2691,22 +2691,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>94464693</t>
+          <t>81952175</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CAUCHOS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>POMARI</t>
+          <t>SOLIER</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DILAN ELIAS</t>
+          <t>JHOMPIO JHOSEP MARC</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>30/11/2025</t>
+          <t>12/05/2020</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,45 +2754,45 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>81952175</t>
+          <t>75935131</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CAUCHOS</t>
+          <t>CCAHUANA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SOLIER</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>JHOMPIO JHOSEP MARC</t>
+          <t>NAHOMY HAYRES</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>12/05/2020</t>
+          <t>16/04/2006</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>12/05/2025</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,45 +2817,45 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>75935131</t>
+          <t>81952235</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CCAHUANA</t>
+          <t>CCORIÑAUPA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NAHOMY HAYRES</t>
+          <t>SAID ALDAIR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>16/04/2006</t>
+          <t>18/09/2020</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/09/2025</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,22 +2880,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>81952235</t>
+          <t>28580685</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CCORIÑAUPA</t>
+          <t>CHAUPIS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>MALCA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAID ALDAIR</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>18/09/2020</t>
+          <t>01/06/1963</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>15/11/2012</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>72377709</t>
+          <t>81952231</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ESPINO</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>SEDANO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RUBEN</t>
+          <t>NYTAN STIVEN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>19/11/2001</t>
+          <t>20/08/2021</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>91717071</t>
+          <t>72377709</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4029,30 +4029,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SHAROL YUNTSU</t>
+          <t>RUBEN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>07/02/2020</t>
+          <t>19/11/2001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>07/02/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>92095116</t>
+          <t>91717071</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HANNAH YOSHYRA</t>
+          <t>SHAROL YUNTSU</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>05/11/2020</t>
+          <t>07/02/2020</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>07/02/2025</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,22 +4140,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>81907107</t>
+          <t>92095116</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>ESPINO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>RICRA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LARA LUANA</t>
+          <t>HANNAH YOSHYRA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>04/08/2020</t>
+          <t>05/11/2020</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,22 +4203,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>81952171</t>
+          <t>81907107</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MARY CRUZ</t>
+          <t>LARA LUANA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4227,11 +4227,11 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>29/01/2021</t>
+          <t>04/08/2020</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>04/08/2025</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,22 +4266,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>92339591</t>
+          <t>81952171</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ARAUJO</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KEYSI ANTONELLA</t>
+          <t>MARY CRUZ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>01/05/2021</t>
+          <t>29/01/2021</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>91883848</t>
+          <t>92339591</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RICSE</t>
+          <t>ARAUJO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>YURLETH JHANCY</t>
+          <t>KEYSI ANTONELLA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,11 +4353,11 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>01/05/2021</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,22 +4392,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>81952186</t>
+          <t>91883848</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CUBA</t>
+          <t>RICSE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CATTLEYA KORAL</t>
+          <t>YURLETH JHANCY</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4416,11 +4416,11 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>22/02/2021</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>22/02/2026</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23716407</t>
+          <t>81952186</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4465,35 +4465,35 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>CUBA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO</t>
+          <t>CATTLEYA KORAL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>04/09/1964</t>
+          <t>22/02/2021</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/02/2026</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,22 +4518,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>71841348</t>
+          <t>23716407</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LEONARDO</t>
+          <t>JORGE ANTONIO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18/10/1993</t>
+          <t>04/09/1964</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>24/11/2020</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,22 +4581,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>91916132</t>
+          <t>71841348</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ROY RUBEN</t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>03/07/2020</t>
+          <t>18/10/1993</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>03/07/2025</t>
+          <t>24/11/2020</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,45 +4644,45 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>60592477</t>
+          <t>91916132</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ALMONACID</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ANGELA MARIANA</t>
+          <t>ROY RUBEN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>31/12/2007</t>
+          <t>03/07/2020</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>03/07/2025</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,40 +4707,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>47385476</t>
+          <t>92512496</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>HIRVIN</t>
+          <t>CRISTEL DANIELA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>26/08/1990</t>
+          <t>28/08/2021</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,45 +4770,45 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>81907115</t>
+          <t>60592477</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HERRERAS</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ALMONACID</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>JOSHUA WERNER</t>
+          <t>ANGELA MARIANA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14/05/2020</t>
+          <t>31/12/2007</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,22 +4833,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>46179701</t>
+          <t>47385476</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>QUINCHORI</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>HIRVIN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>21/02/1990</t>
+          <t>26/08/1990</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,45 +4896,45 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>78104072</t>
+          <t>81907115</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HUALLPA</t>
+          <t>HERRERAS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MALOAYZA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DIANA MELISSA</t>
+          <t>JOSHUA WERNER</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20/10/1997</t>
+          <t>14/05/2020</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,45 +4959,45 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>92092525</t>
+          <t>46179701</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HUALLPA</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>YARANGA</t>
+          <t>QUINCHORI</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>XIANNA SHAMIRA</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>03/11/2020</t>
+          <t>21/02/1990</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>28/08/2025</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,45 +5022,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>94415334</t>
+          <t>78104072</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HUALLPA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ACUÑA</t>
+          <t>MALOAYZA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BRICK JUNIOR</t>
+          <t>DIANA MELISSA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>20/10/1997</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,22 +5085,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>91927453</t>
+          <t>92092525</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HUALLPA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CCARHUAS</t>
+          <t>YARANGA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ANGELA NATZUMI</t>
+          <t>XIANNA SHAMIRA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>12/07/2020</t>
+          <t>03/11/2020</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>12/07/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,7 +5148,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>81952218</t>
+          <t>94415334</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5158,25 +5158,25 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t>ACUÑA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CRISTEL JENNER</t>
+          <t>BRICK JUNIOR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>23/07/2021</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>92489511</t>
+          <t>91927453</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>CCARHUAS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ALITZA XIANNA</t>
+          <t>ANGELA NATZUMI</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>12/07/2020</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>12/07/2025</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>47594292</t>
+          <t>81952218</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VANESSA DORIS</t>
+          <t>CRISTEL JENNER</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>08/09/1991</t>
+          <t>23/07/2021</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>91811180</t>
+          <t>92489511</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5347,25 +5347,25 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DILAN ORIEL</t>
+          <t>ALITZA XIANNA</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>12/04/2020</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>12/04/2025</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>81907102</t>
+          <t>47594292</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5410,35 +5410,35 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USQUIANO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LIAM ADRIAN</t>
+          <t>VANESSA DORIS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>17/10/2020</t>
+          <t>08/09/1991</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,27 +5463,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>91745279</t>
+          <t>91811180</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ROMANI</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SHANIRA MERLIZ ARISUY</t>
+          <t>DILAN ORIEL</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>25/02/2020</t>
+          <t>12/04/2020</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>25/02/2025</t>
+          <t>12/04/2025</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,35 +5526,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>92298999</t>
+          <t>81907102</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>USQUIANO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AMY ABRIL</t>
+          <t>LIAM ADRIAN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>02/04/2021</t>
+          <t>17/10/2020</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,35 +5589,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>91128023</t>
+          <t>91745279</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JACINTO</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LEIVA</t>
+          <t>ROMANI</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>HENRRY EITHAN</t>
+          <t>SHANIRA MERLIZ ARISUY</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>07/01/2019</t>
+          <t>25/02/2020</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>25/02/2025</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,22 +5652,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>91776532</t>
+          <t>92298999</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JANAMPA</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ANAHY BRITANY</t>
+          <t>AMY ABRIL</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5676,11 +5676,11 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>16/03/2020</t>
+          <t>02/04/2021</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>16/03/2025</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>92219594</t>
+          <t>91128023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JANAMPA</t>
+          <t>JACINTO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SULCA</t>
+          <t>LEIVA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AARON EVANS</t>
+          <t>HENRRY EITHAN</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,11 +5739,11 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>04/02/2021</t>
+          <t>07/01/2019</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,22 +5778,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>46733317</t>
+          <t>91776532</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JERI</t>
+          <t>JANAMPA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OLGA</t>
+          <t>ANAHY BRITANY</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5802,16 +5802,16 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>04/06/1991</t>
+          <t>16/03/2020</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>05/10/2012</t>
+          <t>16/03/2025</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>73048949</t>
+          <t>92219594</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>JANAMPA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>SULCA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MIKE FELIPE</t>
+          <t>AARON EVANS</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,16 +5865,16 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>21/12/1993</t>
+          <t>04/02/2021</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,22 +5904,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>92347587</t>
+          <t>46733317</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JUÑURUCO</t>
+          <t>JERI</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CESIA CRISTHEL</t>
+          <t>OLGA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5928,16 +5928,16 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>06/05/2021</t>
+          <t>04/06/1991</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>05/10/2012</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,40 +5967,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>92274576</t>
+          <t>73048949</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LANASCA</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BRITANI BRILLI</t>
+          <t>MIKE FELIPE</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>16/03/2021</t>
+          <t>21/12/1993</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,35 +6030,35 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>81907122</t>
+          <t>92347587</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LAPA</t>
+          <t>JUÑURUCO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CCASANI</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ANDREY SEBASTIAN</t>
+          <t>CESIA CRISTHEL</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>05/06/2020</t>
+          <t>06/05/2021</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>27/06/2025</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,27 +6093,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>81952153</t>
+          <t>92274576</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LAURA</t>
+          <t>LANASCA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AARON JASIEL</t>
+          <t>BRITANI BRILLI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>11/01/2021</t>
+          <t>16/03/2021</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>11/01/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,22 +6156,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>48308607</t>
+          <t>81907122</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>LAPA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GUTIERRES</t>
+          <t>CCASANI</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CARLOS KABELYN</t>
+          <t>ANDREY SEBASTIAN</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6180,16 +6180,16 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>06/04/1994</t>
+          <t>05/06/2020</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>27/06/2025</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>92308432</t>
+          <t>81952153</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>LAURA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DIR DRICK HENRY</t>
+          <t>AARON JASIEL</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>09/04/2021</t>
+          <t>11/01/2021</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/01/2026</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,45 +6282,45 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>81952178</t>
+          <t>48308607</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LLAMASCA</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>GUTIERRES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>YURI YADEL</t>
+          <t>CARLOS KABELYN</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>10/08/2020</t>
+          <t>06/04/1994</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>10/08/2025</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,35 +6345,35 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>94361564</t>
+          <t>92308432</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LOAYZA</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KEILA KALESI</t>
+          <t>DIR DRICK HENRY</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>27/08/2025</t>
+          <t>09/04/2021</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>27/08/2025</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,22 +6408,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>63112593</t>
+          <t>81952178</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LOAYZA</t>
+          <t>LLAMASCA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LUPACA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>FLOR JIMENA SOLANGE</t>
+          <t>YURI YADEL</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6432,21 +6432,21 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>02/01/2012</t>
+          <t>10/08/2020</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>10/08/2025</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,35 +6471,35 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>81993216</t>
+          <t>94361564</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LUNASCO</t>
+          <t>LOAYZA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LENO AUBAMEYANG</t>
+          <t>KEILA KALESI</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>13/08/2020</t>
+          <t>27/08/2025</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>13/08/2025</t>
+          <t>27/08/2025</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>91979701</t>
+          <t>63112593</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LUYA</t>
+          <t>LOAYZA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LAPA</t>
+          <t>LUPACA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>REYSHELL DASHA ACENETH</t>
+          <t>FLOR JIMENA SOLANGE</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>19/08/2020</t>
+          <t>02/01/2012</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,35 +6597,35 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>92408493</t>
+          <t>81993216</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MALLCCO</t>
+          <t>LUNASCO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CARMEN SOFIA</t>
+          <t>LENO AUBAMEYANG</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>17/06/2021</t>
+          <t>13/08/2020</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>13/08/2025</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,22 +6660,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>92069304</t>
+          <t>91979701</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MASHACURI</t>
+          <t>LUYA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>LAPA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AYLHYN RAYSA</t>
+          <t>REYSHELL DASHA ACENETH</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>19/10/2020</t>
+          <t>19/08/2020</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,35 +6723,35 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>81952159</t>
+          <t>92408493</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MALLCCO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ROITH DERECK</t>
+          <t>CARMEN SOFIA</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>18/08/2020</t>
+          <t>17/06/2021</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>18/08/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,22 +6786,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>61036965</t>
+          <t>92069304</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MASHACURI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>AYLHYN RAYSA</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6810,16 +6810,16 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>21/04/2007</t>
+          <t>19/10/2020</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,27 +6849,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>92101549</t>
+          <t>81952159</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DANNA KENSLY IDA</t>
+          <t>ROITH DERECK</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>14/07/2020</t>
+          <t>18/08/2020</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>18/08/2025</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>81952194</t>
+          <t>61036965</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>KEYLA ALESSA</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>11/10/2020</t>
+          <t>21/04/2007</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>22476772</t>
+          <t>92101549</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MERCEDES</t>
+          <t>MENESES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>MARIA</t>
+          <t>DANNA KENSLY IDA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>05/06/1971</t>
+          <t>14/07/2020</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,27 +7038,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>92005854</t>
+          <t>81952194</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MORI</t>
+          <t>MENESES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BANEO</t>
+          <t>ESPINAL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>EDSON</t>
+          <t>KEYLA ALESSA</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>28/08/2020</t>
+          <t>11/10/2020</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,45 +7101,45 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>93693172</t>
+          <t>22476772</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MUCHA</t>
+          <t>MERCEDES</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DYLAN ZAID JOSE</t>
+          <t>MARIA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>21/01/2024</t>
+          <t>05/06/1971</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>29/01/2024</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,35 +7164,35 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>92420729</t>
+          <t>92005854</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MORI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>BANEO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ADISSON LUNA</t>
+          <t>EDSON</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>25/06/2021</t>
+          <t>28/08/2020</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>28/08/2025</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,35 +7227,35 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>92411951</t>
+          <t>93693172</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>MUCHA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>JERI</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DAHNA JHAIFEC</t>
+          <t>DYLAN ZAID JOSE</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20/06/2021</t>
+          <t>21/01/2024</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>29/01/2024</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,45 +7290,45 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>61419547</t>
+          <t>92420729</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>WALTER</t>
+          <t>ADISSON LUNA</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>04/09/2008</t>
+          <t>25/06/2021</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>18/07/2013</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,7 +7353,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>62602011</t>
+          <t>92411951</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7363,35 +7363,35 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>JERI</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>DAHNA JHAIFEC</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>26/04/2010</t>
+          <t>20/06/2021</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>18/07/2013</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,7 +7416,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>81331653</t>
+          <t>61419547</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7431,30 +7431,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>YESICA</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>03/12/2014</t>
+          <t>04/09/2008</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>27/05/2016</t>
+          <t>18/07/2013</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,22 +7479,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>91931802</t>
+          <t>62602011</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ORDOÑEZ</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TAYPE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>JOSUE ANGEL</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>15/07/2020</t>
+          <t>26/04/2010</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>18/07/2013</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,45 +7542,45 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>93559063</t>
+          <t>81331653</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BERROSPI</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DILAN DEREK</t>
+          <t>YESICA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>28/09/2023</t>
+          <t>03/12/2014</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>29/09/2023</t>
+          <t>27/05/2016</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,22 +7605,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>81907123</t>
+          <t>91931802</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>ORDOÑEZ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HUANACO</t>
+          <t>TAYPE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>STEPHEN WILSON</t>
+          <t>JOSUE ANGEL</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20/04/2020</t>
+          <t>15/07/2020</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>20/04/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,7 +7668,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>28282243</t>
+          <t>93559063</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TIFONCIO</t>
+          <t>BERROSPI</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>DILAN DEREK</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,21 +7692,21 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>04/10/1971</t>
+          <t>28/09/2023</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>29/09/2023</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,35 +7731,35 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>92320507</t>
+          <t>81907123</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GRANADOS</t>
+          <t>HUANACO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>JISOO YAMILETH</t>
+          <t>STEPHEN WILSON</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>18/04/2021</t>
+          <t>20/04/2020</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2025</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,45 +7794,45 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>94564900</t>
+          <t>28282243</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ACHA</t>
+          <t>TIFONCIO</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>KEREN SARAI</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>04/10/1971</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,22 +7857,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>93480482</t>
+          <t>92320507</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GRANADOS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ALEXANDRA SOFIA</t>
+          <t>JISOO YAMILETH</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7881,11 +7881,11 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>27/07/2023</t>
+          <t>18/04/2021</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>27/07/2023</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,22 +7920,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>92103095</t>
+          <t>94564900</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PAITAN</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ACHA</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>JASMIN YAMILETH</t>
+          <t>KEREN SARAI</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7944,11 +7944,11 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>09/11/2020</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>09/11/2025</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,35 +7983,35 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>81952166</t>
+          <t>93480482</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>IKER ALEJANDRO</t>
+          <t>ALEXANDRA SOFIA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>30/01/2021</t>
+          <t>27/07/2023</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>27/07/2023</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,45 +8046,45 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>62416726</t>
+          <t>94761959</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>JERI</t>
+          <t>GUERREROS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>MARIELYS ARISBETH</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>16/07/2007</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>05/10/2012</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,22 +8109,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>91362658</t>
+          <t>92103095</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PAITAN</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>JERI</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>KIMBERLY GIORGIA</t>
+          <t>JASMIN YAMILETH</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8133,11 +8133,11 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>10/06/2019</t>
+          <t>09/11/2020</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>10/06/2024</t>
+          <t>09/11/2025</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,45 +8172,45 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>60102393</t>
+          <t>81952166</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PARIAMANCCO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LUZ SHEYLA</t>
+          <t>IKER ALEJANDRO</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>21/05/2005</t>
+          <t>30/01/2021</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>23/12/2025</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,22 +8235,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>81952236</t>
+          <t>62416726</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OROSCO</t>
+          <t>JERI</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DYLAN GABRIEL</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8259,21 +8259,21 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>13/08/2021</t>
+          <t>16/07/2007</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>05/10/2012</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>81952216</t>
+          <t>91362658</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PILLACA</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>INTIQUILLA</t>
+          <t>JERI</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ALEJANDRA</t>
+          <t>KIMBERLY GIORGIA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,11 +8322,11 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>27/05/2020</t>
+          <t>10/06/2019</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>10/06/2024</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,22 +8361,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>91779056</t>
+          <t>60102393</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>POLANCO</t>
+          <t>PARIAMANCCO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>HANNA KATALEYA</t>
+          <t>LUZ SHEYLA</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8385,21 +8385,21 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>17/03/2020</t>
+          <t>21/05/2005</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>17/03/2025</t>
+          <t>23/12/2025</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,22 +8424,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>93537830</t>
+          <t>81952236</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>POZO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>OROSCO</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ALEXIS JHON</t>
+          <t>DYLAN GABRIEL</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8448,11 +8448,11 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>23/03/2020</t>
+          <t>13/08/2021</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>23/03/2025</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,27 +8487,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>92035969</t>
+          <t>81952216</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>PILLACA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>INTIQUILLA</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DILAN GAEL</t>
+          <t>ALEJANDRA</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>27/09/2020</t>
+          <t>27/05/2020</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>27/09/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,22 +8550,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>92018669</t>
+          <t>91779056</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>POLANCO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BAEZ</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ALISSON MIREYA</t>
+          <t>HANNA KATALEYA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>16/09/2020</t>
+          <t>17/03/2020</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>17/03/2025</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,27 +8613,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>81952156</t>
+          <t>93537830</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>POZO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LAGO</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NAYSHA ISAMAR</t>
+          <t>ALEXIS JHON</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>12/12/2020</t>
+          <t>23/03/2020</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>23/03/2025</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,22 +8676,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>81907106</t>
+          <t>92035969</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>THOMAS ALBARO</t>
+          <t>DILAN GAEL</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>29/09/2020</t>
+          <t>27/09/2020</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>27/09/2025</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>91736037</t>
+          <t>92018669</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>BAEZ</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>KAYRA CLEYDI</t>
+          <t>ALISSON MIREYA</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>19/02/2020</t>
+          <t>16/09/2020</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>19/02/2025</t>
+          <t>16/09/2025</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,35 +8802,35 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>94263521</t>
+          <t>81952156</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CHIHUA</t>
+          <t>LAGO</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>IKER JAZIEL</t>
+          <t>NAYSHA ISAMAR</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>12/12/2020</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,35 +8865,35 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>92229552</t>
+          <t>81907106</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>RUTH MISSHELL</t>
+          <t>THOMAS ALBARO</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>11/02/2021</t>
+          <t>29/09/2020</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,35 +8928,35 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>92328541</t>
+          <t>91736037</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>EDRIC MAURICIO</t>
+          <t>KAYRA CLEYDI</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>23/04/2021</t>
+          <t>19/02/2020</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>19/02/2025</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,27 +8991,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>92409162</t>
+          <t>92497371</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CHOCÑA</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OSIEL EMILEC</t>
+          <t>TAITH VALENTINA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>18/06/2021</t>
+          <t>17/08/2021</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,22 +9054,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>81952223</t>
+          <t>94263521</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>CHIHUA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LOLO</t>
+          <t>IKER JAZIEL</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9078,11 +9078,11 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>04/06/2021</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,22 +9117,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>94384573</t>
+          <t>92229552</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SULY</t>
+          <t>RUTH MISSHELL</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9141,11 +9141,11 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>13/09/2025</t>
+          <t>11/02/2021</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,22 +9180,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>71054501</t>
+          <t>92328541</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>SEGUNDO GUILLERMO</t>
+          <t>EDRIC MAURICIO</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9204,21 +9204,21 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>04/05/1997</t>
+          <t>23/04/2021</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,22 +9243,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>92275464</t>
+          <t>92409162</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>REVOLLAR</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CERAS</t>
+          <t>CHOCÑA</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>DAYMER WILSON</t>
+          <t>OSIEL EMILEC</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>17/03/2021</t>
+          <t>18/06/2021</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9306,35 +9306,35 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>94742703</t>
+          <t>81952223</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RIMAYCUNA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>BRENDA ARACELI</t>
+          <t>LOLO</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>04/06/2021</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9369,22 +9369,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>91830656</t>
+          <t>94384573</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ROCA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LISBETH ANIELA</t>
+          <t>SULY</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9393,11 +9393,11 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>27/04/2020</t>
+          <t>13/09/2025</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>27/04/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9432,45 +9432,45 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>92121034</t>
+          <t>71054501</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>BRIZETH ZAYURI</t>
+          <t>SEGUNDO GUILLERMO</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>21/11/2020</t>
+          <t>04/05/1997</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9495,35 +9495,35 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>92175169</t>
+          <t>92275464</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>REVOLLAR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ZANABRIA</t>
+          <t>CERAS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>FERIDE MERIDA KIKYO</t>
+          <t>DAYMER WILSON</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>30/12/2020</t>
+          <t>17/03/2021</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>30/12/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9558,35 +9558,35 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>93546566</t>
+          <t>94742703</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>RIMAYCUNA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BLACIDO</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>OLIVER JAMES</t>
+          <t>BRENDA ARACELI</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>21/09/2023</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9621,22 +9621,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>94203849</t>
+          <t>92480380</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>RISCO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>YAETH LIONEL</t>
+          <t>FATMIR VICTORDANIEL</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9645,11 +9645,11 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>07/04/2025</t>
+          <t>06/08/2021</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9684,22 +9684,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>81952190</t>
+          <t>91830656</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>ROCA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>RICRA</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ALESSIA ABIGAIL</t>
+          <t>LISBETH ANIELA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>15/03/2021</t>
+          <t>27/04/2020</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>27/04/2025</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9747,22 +9747,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>81952167</t>
+          <t>92121034</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ZALESKI YAZURI</t>
+          <t>BRIZETH ZAYURI</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9771,11 +9771,11 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>16/01/2021</t>
+          <t>21/11/2020</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9810,22 +9810,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>81907141</t>
+          <t>92175169</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>POMA</t>
+          <t>ZANABRIA</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ANNA SARAI</t>
+          <t>FERIDE MERIDA KIKYO</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20/06/2020</t>
+          <t>30/12/2020</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>20/06/2025</t>
+          <t>30/12/2025</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9873,45 +9873,45 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>44239287</t>
+          <t>93546566</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>BLACIDO</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LIONESA</t>
+          <t>OLIVER JAMES</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>07/02/1986</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>18/07/2013</t>
+          <t>21/09/2023</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9936,22 +9936,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>91805861</t>
+          <t>94203849</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>STEVEN SNEYGER</t>
+          <t>YAETH LIONEL</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>07/04/2020</t>
+          <t>07/04/2025</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>07/04/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9999,27 +9999,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>81952200</t>
+          <t>81952190</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SHARETTE</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>AARON DARIEL JACK</t>
+          <t>ALESSIA ABIGAIL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>17/01/2021</t>
+          <t>15/03/2021</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>15/03/2026</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10062,22 +10062,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>94314109</t>
+          <t>81952167</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SHINTSIA</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CALLUPE</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>AILANIA ZARIAH</t>
+          <t>ZALESKI YAZURI</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -10086,11 +10086,11 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>16/01/2021</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>16/08/2025</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10125,35 +10125,35 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>93473010</t>
+          <t>92522714</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SHUMPATE</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ALMONACID</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LIAN JARET</t>
+          <t>JASMIN ANTONELLA</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>19/07/2023</t>
+          <t>04/09/2021</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>29/07/2023</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10188,45 +10188,45 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>44449848</t>
+          <t>81907141</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SHUMPATE</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CAYSAHUANA</t>
+          <t>POMA</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>ANNA SARAI</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>23/10/1981</t>
+          <t>20/06/2020</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>20/06/2025</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10251,35 +10251,35 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>91749480</t>
+          <t>92465800</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SULCA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>GASTELU</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DAYIRO JAIRO</t>
+          <t>ANYELY CINDY LIZANDRA</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>27/02/2020</t>
+          <t>26/07/2021</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10314,45 +10314,45 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>81952212</t>
+          <t>44239287</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TARAZONA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>AXEL MARIANO</t>
+          <t>LIONESA</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>03/10/2020</t>
+          <t>07/02/1986</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>18/07/2013</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10377,27 +10377,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>91964630</t>
+          <t>91805861</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MARQUINA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>BRITTANY ARACELY</t>
+          <t>STEVEN SNEYGER</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>09/08/2020</t>
+          <t>07/04/2020</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>09/08/2025</t>
+          <t>07/04/2025</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10440,22 +10440,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>43118682</t>
+          <t>81952200</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>SHARETTE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>FIDEL</t>
+          <t>AARON DARIEL JACK</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10464,21 +10464,21 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>16/08/1983</t>
+          <t>17/01/2021</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>17/01/2026</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10503,22 +10503,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>92146515</t>
+          <t>94314109</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>SHINTSIA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>CALLUPE</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>HEYDI NURIA</t>
+          <t>AILANIA ZARIAH</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10527,11 +10527,11 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>09/12/2020</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>16/08/2025</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10566,22 +10566,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>81952161</t>
+          <t>93473010</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TENORIO</t>
+          <t>SHUMPATE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t>ALMONACID</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>JHON KEVIN</t>
+          <t>LIAN JARET</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10590,11 +10590,11 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>14/06/2020</t>
+          <t>19/07/2023</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>14/06/2025</t>
+          <t>29/07/2023</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10629,22 +10629,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>94245663</t>
+          <t>44449848</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TERRAZA</t>
+          <t>SHUMPATE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BARBARAN</t>
+          <t>CAYSAHUANA</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LIAM ALEXANDER</t>
+          <t>EVER</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10653,21 +10653,21 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>23/10/1981</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10692,22 +10692,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>81952173</t>
+          <t>91749480</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TERRAZA</t>
+          <t>SULCA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>CAÑAVI</t>
+          <t>GASTELU</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>DERECK ALEJANDRO</t>
+          <t>DAYIRO JAIRO</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>11/09/2020</t>
+          <t>27/02/2020</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10755,22 +10755,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>81907104</t>
+          <t>93107220</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TERRES</t>
+          <t>TANANTA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>QUINCHUNGA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>HAIT DYLAN</t>
+          <t>YONSEO</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10779,11 +10779,11 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>09/10/2020</t>
+          <t>07/09/2021</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10818,35 +10818,35 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>92293798</t>
+          <t>81952212</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TARAZONA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>YAMELY MADAITH</t>
+          <t>AXEL MARIANO</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>29/03/2021</t>
+          <t>03/10/2020</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>29/03/2026</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10881,35 +10881,35 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>92228104</t>
+          <t>91964630</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MARQUINA</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>JHONJAIRO ALEXIS</t>
+          <t>BRITTANY ARACELY</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>10/02/2021</t>
+          <t>09/08/2020</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>09/08/2025</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10944,22 +10944,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>81952195</t>
+          <t>43118682</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TOSCANO</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>GERALD ANDREWS</t>
+          <t>FIDEL</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10968,21 +10968,21 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>16/07/2020</t>
+          <t>16/08/1983</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -11007,35 +11007,35 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>92351412</t>
+          <t>92146515</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>UCHARIMA</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>JESUS GAEL</t>
+          <t>HEYDI NURIA</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>09/05/2021</t>
+          <t>09/12/2020</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11070,22 +11070,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>49077400</t>
+          <t>81952161</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>TENORIO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>CHORIHUANTE</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ROSSEL</t>
+          <t>JHON KEVIN</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11094,21 +11094,21 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>01/01/1989</t>
+          <t>14/06/2020</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>14/06/2025</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11133,22 +11133,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>91868247</t>
+          <t>94245663</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>TERRAZA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ACUÑA</t>
+          <t>BARBARAN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>CARLOS ARJUNS</t>
+          <t>LIAM ALEXANDER</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -11157,11 +11157,11 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>26/05/2020</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11196,22 +11196,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>81952165</t>
+          <t>81952173</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>TERRAZA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CHUJUTALLI</t>
+          <t>CAÑAVI</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>JESUS ERIK JHON</t>
+          <t>DERECK ALEJANDRO</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -11220,11 +11220,11 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>11/09/2020</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11259,22 +11259,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>91733773</t>
+          <t>81907104</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>VENANCINO</t>
+          <t>TERRES</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>QUINCHUNGA</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AZIEL</t>
+          <t>HAIT DYLAN</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>18/02/2020</t>
+          <t>09/10/2020</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11322,22 +11322,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>94674241</t>
+          <t>92293798</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>VERA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>YAMUNAQUE</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ITZEL ANTONELLA</t>
+          <t>YAMELY MADAITH</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11346,11 +11346,11 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>29/03/2021</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>29/03/2026</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11385,22 +11385,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>92257077</t>
+          <t>92228104</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ROBERTH EFRAIN</t>
+          <t>JHONJAIRO ALEXIS</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>03/03/2021</t>
+          <t>10/02/2021</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11448,35 +11448,35 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>92250111</t>
+          <t>81952195</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>VILLARRUEL</t>
+          <t>TOSCANO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CCANCCE</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>YISEL ANGELA</t>
+          <t>GERALD ANDREWS</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>27/02/2021</t>
+          <t>16/07/2020</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11511,22 +11511,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>81952191</t>
+          <t>92351412</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YACHA</t>
+          <t>UCHARIMA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LLANTOY</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NAIN BEZAEEL</t>
+          <t>JESUS GAEL</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>04/03/2021</t>
+          <t>09/05/2021</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11574,22 +11574,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>81952179</t>
+          <t>49077400</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YANGARI</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>NOLBERTO</t>
+          <t>CHORIHUANTE</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ALDAIR JHUSUA</t>
+          <t>ROSSEL</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11598,16 +11598,16 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>04/10/2020</t>
+          <t>01/01/1989</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11637,22 +11637,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>92402917</t>
+          <t>91868247</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YAURI</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MACHAO</t>
+          <t>ACUÑA</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>MATTHEW HARMAN</t>
+          <t>CARLOS ARJUNS</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11661,11 +11661,11 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>14/06/2021</t>
+          <t>26/05/2020</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11700,35 +11700,35 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>81907124</t>
+          <t>81952165</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YULGO</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>CHUJUTALLI</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NAOMI ADALIS</t>
+          <t>JESUS ERIK JHON</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>21/06/2020</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11763,22 +11763,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>81780145</t>
+          <t>91733773</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ÑACO</t>
+          <t>VENANCINO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>GOMES</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ELMER</t>
+          <t>AZIEL</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>17/05/2020</t>
+          <t>18/02/2020</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11826,63 +11826,567 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
+          <t>94674241</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>VERA</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>YAMUNAQUE</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ITZEL ANTONELLA</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>VIZCATAN DEL ENE</t>
+        </is>
+      </c>
+      <c r="M182" t="n">
+        <v>120609</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>92257077</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>HUAMANI</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ROBERTH EFRAIN</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>5</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>03/03/2021</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>VIZCATAN DEL ENE</t>
+        </is>
+      </c>
+      <c r="M183" t="n">
+        <v>120609</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>92250111</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>VILLARRUEL</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CCANCCE</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>YISEL ANGELA</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>5</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>27/02/2021</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>VIZCATAN DEL ENE</t>
+        </is>
+      </c>
+      <c r="M184" t="n">
+        <v>120609</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>81952191</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>YACHA</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>LLANTOY</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NAIN BEZAEEL</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>5</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>04/03/2021</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>VIZCATAN DEL ENE</t>
+        </is>
+      </c>
+      <c r="M185" t="n">
+        <v>120609</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>81952179</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>YANGARI</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>NOLBERTO</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ALDAIR JHUSUA</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>6</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>04/10/2020</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>VIZCATAN DEL ENE</t>
+        </is>
+      </c>
+      <c r="M186" t="n">
+        <v>120609</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>92402917</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>YAURI</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>MACHAO</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>MATTHEW HARMAN</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>5</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>14/06/2021</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>VIZCATAN DEL ENE</t>
+        </is>
+      </c>
+      <c r="M187" t="n">
+        <v>120609</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>81907124</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>YULGO</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>GUZMAN</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NAOMI ADALIS</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>6</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>21/06/2020</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>30/07/2025</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>VIZCATAN DEL ENE</t>
+        </is>
+      </c>
+      <c r="M188" t="n">
+        <v>120609</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>81780145</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>ÑACO</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>GOMES</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ELMER</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>6</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>17/05/2020</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>AFILIACION MASIVA DE OFICIO</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>27/05/2025</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>VIZCATAN DEL ENE</t>
+        </is>
+      </c>
+      <c r="M189" t="n">
+        <v>120609</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
           <t>81907139</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>ÑAÑA</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>CHIMAYCO</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>LIAN</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E190" t="inlineStr">
         <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F182" t="n">
+      <c r="F190" t="n">
         <v>6</v>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G190" t="inlineStr">
         <is>
           <t>09/07/2020</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
         <is>
           <t>AFILIACION PPDD</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
         <is>
           <t>09/07/2025</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>VIZCATAN DEL ENE</t>
-        </is>
-      </c>
-      <c r="M182" t="n">
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>VIZCATAN DEL ENE</t>
+        </is>
+      </c>
+      <c r="M190" t="n">
         <v>120609</v>
       </c>
     </row>

--- a/exports/32840_paquichari.xlsx
+++ b/exports/32840_paquichari.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,22 +738,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>91773557</t>
+          <t>91808823</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>AIQUIPA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PAQUIYAURI</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JHOSELIN</t>
+          <t>ALEXIA ANGHELINA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>13/03/2020</t>
+          <t>09/04/2020</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>13/03/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -801,22 +801,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>45466806</t>
+          <t>23382349</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ALMONACID</t>
+          <t>ALANYA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>QUINTO</t>
+          <t>ARAUJO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NOELIA</t>
+          <t>SANTA TEREZA MARUJA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20/01/1988</t>
+          <t>15/10/1970</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20/03/2015</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -864,27 +864,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>91703633</t>
+          <t>91773557</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALTAMIRANO</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>PAQUIYAURI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RUSSER EMIR</t>
+          <t>JHOSELIN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29/01/2020</t>
+          <t>13/03/2020</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>29/01/2025</t>
+          <t>13/03/2025</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -927,22 +927,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>91983316</t>
+          <t>45466806</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ANYOSA</t>
+          <t>ALMONACID</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>QUINTO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RUTH INES</t>
+          <t>NOELIA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23/08/2020</t>
+          <t>20/01/1988</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23/08/2025</t>
+          <t>20/03/2015</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -990,22 +990,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>74174339</t>
+          <t>91703633</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARAUJO</t>
+          <t>ALTAMIRANO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RINZON</t>
+          <t>RUSSER EMIR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22/06/1996</t>
+          <t>29/01/2020</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>06/03/2024</t>
+          <t>29/01/2025</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1053,27 +1053,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>92318026</t>
+          <t>91983316</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARMAS</t>
+          <t>ANYOSA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NELSON VALENTINO</t>
+          <t>RUTH INES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15/12/2020</t>
+          <t>23/08/2020</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>23/08/2025</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1116,22 +1116,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>81952183</t>
+          <t>74174339</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATAO</t>
+          <t>ARAUJO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JULIO JHAFDET</t>
+          <t>RINZON</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>09/05/2020</t>
+          <t>22/06/1996</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>06/03/2024</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1179,45 +1179,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>42650507</t>
+          <t>92318026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ATAO</t>
+          <t>ARMAS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JOHANA</t>
+          <t>NELSON VALENTINO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/10/1983</t>
+          <t>15/12/2020</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1242,22 +1242,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>81767918</t>
+          <t>81952183</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AUQUI</t>
+          <t>ATAO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ISAK ISMAEL</t>
+          <t>JULIO JHAFDET</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13/04/2021</t>
+          <t>09/05/2020</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1305,35 +1305,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>77708148</t>
+          <t>42650507</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>ATAO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CORPUS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t>JOHANA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11/09/1996</t>
+          <t>19/10/1983</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1368,22 +1368,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>92245541</t>
+          <t>81767918</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>AUQUI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AARON JHOAN</t>
+          <t>ISAK ISMAEL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>24/02/2021</t>
+          <t>13/04/2021</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,7 +1431,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>43827868</t>
+          <t>77708148</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>CORPUS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ORLANDO PAUL</t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1455,11 +1455,11 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>08/04/1980</t>
+          <t>11/09/1996</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1494,35 +1494,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>94165960</t>
+          <t>92245541</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BARRA</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CCORIMANYA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BRIYITH XIMENA</t>
+          <t>AARON JHOAN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>24/02/2021</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1557,22 +1557,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>81952189</t>
+          <t>43827868</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BASTIDAS</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WILDER YANDEL</t>
+          <t>ORLANDO PAUL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>24/10/2020</t>
+          <t>08/04/1980</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1620,27 +1620,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>94416220</t>
+          <t>94165960</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>BARRA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OCHANTE</t>
+          <t>CCORIMANYA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CALEB GABRIEL</t>
+          <t>BRIYITH XIMENA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>07/03/2025</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23/12/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1683,27 +1683,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>91731887</t>
+          <t>81952189</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>BASTIDAS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HUARCAYA</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LUHANA</t>
+          <t>WILDER YANDEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>16/02/2020</t>
+          <t>24/10/2020</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>16/02/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1746,22 +1746,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>40828403</t>
+          <t>94416220</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BONIFACIO</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>OCHANTE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO</t>
+          <t>CALEB GABRIEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/11/1979</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>23/12/2025</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1809,35 +1809,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>92440477</t>
+          <t>91731887</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CABALLERO</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PILLACA</t>
+          <t>HUARCAYA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DIEGO LEONEL</t>
+          <t>LUHANA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>08/07/2021</t>
+          <t>16/02/2020</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>16/02/2025</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1872,22 +1872,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>48573984</t>
+          <t>40828403</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CANTORIN</t>
+          <t>BONIFACIO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USCAMAYTA</t>
+          <t>HIDALGO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LEANDRO</t>
+          <t>JOSE ANTONIO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,11 +1896,11 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>02/05/1989</t>
+          <t>05/11/1979</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1935,35 +1935,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>94012660</t>
+          <t>92440477</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>CABALLERO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>PILLACA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KAORI AITANA</t>
+          <t>DIEGO LEONEL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18/10/2024</t>
+          <t>08/07/2021</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,22 +1998,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>72489411</t>
+          <t>48573984</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CANTORIN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CUSICHE</t>
+          <t>USCAMAYTA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>LEANDRO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17/12/1994</t>
+          <t>02/05/1989</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,22 +2061,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>94245502</t>
+          <t>94012660</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LANDEO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ELIANA AYELET</t>
+          <t>KAORI AITANA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2085,11 +2085,11 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>18/10/2024</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>81952238</t>
+          <t>72489411</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CUSICHE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JARRY JAESON</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>09/09/2021</t>
+          <t>17/12/1994</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>81952206</t>
+          <t>94245502</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2197,25 +2197,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YARANGA</t>
+          <t>LANDEO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BEK MAYKER</t>
+          <t>ELIANA AYELET</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14/08/2020</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>14/08/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,27 +2250,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>91817312</t>
+          <t>81952206</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CARRASCO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ALCCA</t>
+          <t>YARANGA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RUTH KIA</t>
+          <t>BEK MAYKER</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>16/04/2020</t>
+          <t>14/08/2020</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>16/04/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,22 +2313,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>92424584</t>
+          <t>91817312</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CASAFRANCA</t>
+          <t>CARRASCO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>ALCCA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MAYA YESHLEN</t>
+          <t>RUTH KIA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>28/06/2021</t>
+          <t>16/04/2020</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>28/06/2026</t>
+          <t>16/04/2025</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,22 +2376,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>91690354</t>
+          <t>92424584</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CASAS</t>
+          <t>CASAFRANCA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SUSAN MARIA</t>
+          <t>MAYA YESHLEN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,11 +2400,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20/01/2020</t>
+          <t>28/06/2021</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,22 +2439,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>90422154</t>
+          <t>91690354</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>CASAS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UNCHUPAICO</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KATALINA ISABELA</t>
+          <t>SUSAN MARIA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2463,11 +2463,11 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22/09/2017</t>
+          <t>20/01/2020</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,22 +2502,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>92158269</t>
+          <t>90422154</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>UNCHUPAICO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LUCIANA DEYANIRA</t>
+          <t>KATALINA ISABELA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2526,11 +2526,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10/11/2020</t>
+          <t>22/09/2017</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>92100040</t>
+          <t>92158269</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CARPIO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>YOR DYLAN SAID</t>
+          <t>LUCIANA DEYANIRA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>08/11/2020</t>
+          <t>10/11/2020</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,7 +2628,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>94464693</t>
+          <t>92100040</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>POMARI</t>
+          <t>CARPIO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DILAN ELIAS</t>
+          <t>YOR DYLAN SAID</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2652,11 +2652,11 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>30/11/2025</t>
+          <t>08/11/2020</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2691,22 +2691,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>81952175</t>
+          <t>94464693</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CAUCHOS</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SOLIER</t>
+          <t>POMARI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JHOMPIO JHOSEP MARC</t>
+          <t>DILAN ELIAS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>12/05/2020</t>
+          <t>30/11/2025</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>12/05/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,45 +2754,45 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>75935131</t>
+          <t>81952175</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CCAHUANA</t>
+          <t>CAUCHOS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t>SOLIER</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NAHOMY HAYRES</t>
+          <t>JHOMPIO JHOSEP MARC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>16/04/2006</t>
+          <t>12/05/2020</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,45 +2817,45 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>81952235</t>
+          <t>75935131</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CCORIÑAUPA</t>
+          <t>CCAHUANA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAID ALDAIR</t>
+          <t>NAHOMY HAYRES</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18/09/2020</t>
+          <t>16/04/2006</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,22 +2880,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>28580685</t>
+          <t>81952235</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CHAUPIS</t>
+          <t>CCORIÑAUPA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MALCA</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>SAID ALDAIR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01/06/1963</t>
+          <t>18/09/2020</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>15/11/2012</t>
+          <t>18/09/2025</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>81952231</t>
+          <t>72377709</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>ESPINO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SEDANO</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NYTAN STIVEN</t>
+          <t>RUBEN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20/08/2021</t>
+          <t>19/11/2001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>72377709</t>
+          <t>91717071</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4029,30 +4029,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RUBEN</t>
+          <t>SHAROL YUNTSU</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19/11/2001</t>
+          <t>07/02/2020</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>07/02/2025</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>91717071</t>
+          <t>92095116</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>RICRA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SHAROL YUNTSU</t>
+          <t>HANNAH YOSHYRA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>07/02/2020</t>
+          <t>05/11/2020</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>07/02/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,22 +4140,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>92095116</t>
+          <t>81907107</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ESPINO</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HANNAH YOSHYRA</t>
+          <t>LARA LUANA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>05/11/2020</t>
+          <t>04/08/2020</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>04/08/2025</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,22 +4203,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>81907107</t>
+          <t>81952171</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LARA LUANA</t>
+          <t>MARY CRUZ</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4227,11 +4227,11 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>04/08/2020</t>
+          <t>29/01/2021</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,22 +4266,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>81952171</t>
+          <t>92339591</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>ARAUJO</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MARY CRUZ</t>
+          <t>KEYSI ANTONELLA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>29/01/2021</t>
+          <t>01/05/2021</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>92339591</t>
+          <t>91883848</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ARAUJO</t>
+          <t>RICSE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KEYSI ANTONELLA</t>
+          <t>YURLETH JHANCY</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,11 +4353,11 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>01/05/2021</t>
+          <t>08/06/2020</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>08/06/2025</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,22 +4392,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>91883848</t>
+          <t>81952186</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RICSE</t>
+          <t>CUBA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>YURLETH JHANCY</t>
+          <t>CATTLEYA KORAL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4416,11 +4416,11 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>08/06/2020</t>
+          <t>22/02/2021</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>08/06/2025</t>
+          <t>22/02/2026</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>81952186</t>
+          <t>23716407</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4465,35 +4465,35 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CUBA</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CATTLEYA KORAL</t>
+          <t>JORGE ANTONIO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>22/02/2021</t>
+          <t>04/09/1964</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>22/02/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,22 +4518,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23716407</t>
+          <t>71841348</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO</t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>04/09/1964</t>
+          <t>18/10/1993</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>24/11/2020</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,22 +4581,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>71841348</t>
+          <t>91916132</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LEONARDO</t>
+          <t>ROY RUBEN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18/10/1993</t>
+          <t>03/07/2020</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>24/11/2020</t>
+          <t>03/07/2025</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,45 +4644,45 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>91916132</t>
+          <t>60592477</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ALMONACID</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ROY RUBEN</t>
+          <t>ANGELA MARIANA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>03/07/2020</t>
+          <t>31/12/2007</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>03/07/2025</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,40 +4707,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>92512496</t>
+          <t>47385476</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GUERRA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CRISTEL DANIELA</t>
+          <t>HIRVIN</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>28/08/2021</t>
+          <t>26/08/1990</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,45 +4770,45 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>60592477</t>
+          <t>81907115</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>HERRERAS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ALMONACID</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ANGELA MARIANA</t>
+          <t>JOSHUA WERNER</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>31/12/2007</t>
+          <t>14/05/2020</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,22 +4833,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>47385476</t>
+          <t>46179701</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>QUINCHORI</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>HIRVIN</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>26/08/1990</t>
+          <t>21/02/1990</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>28/08/2025</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,45 +4896,45 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>81907115</t>
+          <t>78104072</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HERRERAS</t>
+          <t>HUALLPA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MALOAYZA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>JOSHUA WERNER</t>
+          <t>DIANA MELISSA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14/05/2020</t>
+          <t>20/10/1997</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,45 +4959,45 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>46179701</t>
+          <t>92092525</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>HUALLPA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>QUINCHORI</t>
+          <t>YARANGA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>XIANNA SHAMIRA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>21/02/1990</t>
+          <t>03/11/2020</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,45 +5022,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>78104072</t>
+          <t>94415334</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HUALLPA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MALOAYZA</t>
+          <t>ACUÑA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DIANA MELISSA</t>
+          <t>BRICK JUNIOR</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20/10/1997</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,22 +5085,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>92092525</t>
+          <t>91927453</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HUALLPA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>YARANGA</t>
+          <t>CCARHUAS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>XIANNA SHAMIRA</t>
+          <t>ANGELA NATZUMI</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>03/11/2020</t>
+          <t>12/07/2020</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>12/07/2025</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,7 +5148,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>94415334</t>
+          <t>81952218</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5158,25 +5158,25 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ACUÑA</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BRICK JUNIOR</t>
+          <t>CRISTEL JENNER</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>23/07/2021</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>91927453</t>
+          <t>92489511</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CCARHUAS</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ANGELA NATZUMI</t>
+          <t>ALITZA XIANNA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>12/07/2020</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>12/07/2025</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>81952218</t>
+          <t>47594292</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CRISTEL JENNER</t>
+          <t>VANESSA DORIS</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>23/07/2021</t>
+          <t>08/09/1991</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>92489511</t>
+          <t>91811180</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5347,25 +5347,25 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ALITZA XIANNA</t>
+          <t>DILAN ORIEL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>12/04/2020</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>12/04/2025</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>47594292</t>
+          <t>81907102</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5410,35 +5410,35 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>USQUIANO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VANESSA DORIS</t>
+          <t>LIAM ADRIAN</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>08/09/1991</t>
+          <t>17/10/2020</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,27 +5463,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>91811180</t>
+          <t>91745279</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>ROMANI</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DILAN ORIEL</t>
+          <t>SHANIRA MERLIZ ARISUY</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>12/04/2020</t>
+          <t>25/02/2020</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>12/04/2025</t>
+          <t>25/02/2025</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,35 +5526,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>81907102</t>
+          <t>92298999</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USQUIANO</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LIAM ADRIAN</t>
+          <t>AMY ABRIL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>17/10/2020</t>
+          <t>02/04/2021</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,35 +5589,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>91745279</t>
+          <t>91128023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>JACINTO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ROMANI</t>
+          <t>LEIVA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SHANIRA MERLIZ ARISUY</t>
+          <t>HENRRY EITHAN</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>25/02/2020</t>
+          <t>07/01/2019</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>25/02/2025</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,22 +5652,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>92298999</t>
+          <t>91776532</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>JANAMPA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AMY ABRIL</t>
+          <t>ANAHY BRITANY</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5676,11 +5676,11 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>02/04/2021</t>
+          <t>16/03/2020</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>16/03/2025</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>91128023</t>
+          <t>92219594</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JACINTO</t>
+          <t>JANAMPA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LEIVA</t>
+          <t>SULCA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>HENRRY EITHAN</t>
+          <t>AARON EVANS</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,11 +5739,11 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>07/01/2019</t>
+          <t>04/02/2021</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,22 +5778,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>91776532</t>
+          <t>46733317</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JANAMPA</t>
+          <t>JERI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ANAHY BRITANY</t>
+          <t>OLGA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5802,16 +5802,16 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>16/03/2020</t>
+          <t>04/06/1991</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>16/03/2025</t>
+          <t>05/10/2012</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>92219594</t>
+          <t>73048949</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JANAMPA</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SULCA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AARON EVANS</t>
+          <t>MIKE FELIPE</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,16 +5865,16 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>04/02/2021</t>
+          <t>21/12/1993</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,22 +5904,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>46733317</t>
+          <t>92347587</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JERI</t>
+          <t>JUÑURUCO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>OLGA</t>
+          <t>CESIA CRISTHEL</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5928,16 +5928,16 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>04/06/1991</t>
+          <t>06/05/2021</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>05/10/2012</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,40 +5967,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>73048949</t>
+          <t>92274576</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>LANASCA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>MIKE FELIPE</t>
+          <t>BRITANI BRILLI</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>21/12/1993</t>
+          <t>16/03/2021</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,35 +6030,35 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>92347587</t>
+          <t>81907122</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JUÑURUCO</t>
+          <t>LAPA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>CCASANI</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CESIA CRISTHEL</t>
+          <t>ANDREY SEBASTIAN</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>06/05/2021</t>
+          <t>05/06/2020</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/06/2025</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,27 +6093,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>92274576</t>
+          <t>81952153</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LANASCA</t>
+          <t>LAURA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BRITANI BRILLI</t>
+          <t>AARON JASIEL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>16/03/2021</t>
+          <t>11/01/2021</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>11/01/2026</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,22 +6156,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>81907122</t>
+          <t>48308607</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LAPA</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CCASANI</t>
+          <t>GUTIERRES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ANDREY SEBASTIAN</t>
+          <t>CARLOS KABELYN</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6180,16 +6180,16 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>05/06/2020</t>
+          <t>06/04/1994</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>27/06/2025</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>81952153</t>
+          <t>92308432</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LAURA</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AARON JASIEL</t>
+          <t>DIR DRICK HENRY</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>11/01/2021</t>
+          <t>09/04/2021</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>11/01/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,45 +6282,45 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>48308607</t>
+          <t>81952178</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>LLAMASCA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GUTIERRES</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CARLOS KABELYN</t>
+          <t>YURI YADEL</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>06/04/1994</t>
+          <t>10/08/2020</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>10/08/2025</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,35 +6345,35 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>92308432</t>
+          <t>94361564</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>LOAYZA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DIR DRICK HENRY</t>
+          <t>KEILA KALESI</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>09/04/2021</t>
+          <t>27/08/2025</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>27/08/2025</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,22 +6408,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>81952178</t>
+          <t>63112593</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LLAMASCA</t>
+          <t>LOAYZA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>LUPACA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>YURI YADEL</t>
+          <t>FLOR JIMENA SOLANGE</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6432,21 +6432,21 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>10/08/2020</t>
+          <t>02/01/2012</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>10/08/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,35 +6471,35 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>94361564</t>
+          <t>81993216</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LOAYZA</t>
+          <t>LUNASCO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KEILA KALESI</t>
+          <t>LENO AUBAMEYANG</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>27/08/2025</t>
+          <t>13/08/2020</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>27/08/2025</t>
+          <t>13/08/2025</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>63112593</t>
+          <t>91979701</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LOAYZA</t>
+          <t>LUYA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LUPACA</t>
+          <t>LAPA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>FLOR JIMENA SOLANGE</t>
+          <t>REYSHELL DASHA ACENETH</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>02/01/2012</t>
+          <t>19/08/2020</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,35 +6597,35 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>81993216</t>
+          <t>92408493</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LUNASCO</t>
+          <t>MALLCCO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LENO AUBAMEYANG</t>
+          <t>CARMEN SOFIA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>13/08/2020</t>
+          <t>17/06/2021</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>13/08/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,22 +6660,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>91979701</t>
+          <t>92069304</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LUYA</t>
+          <t>MASHACURI</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LAPA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>REYSHELL DASHA ACENETH</t>
+          <t>AYLHYN RAYSA</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>19/08/2020</t>
+          <t>19/10/2020</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,35 +6723,35 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>92408493</t>
+          <t>81952159</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MALLCCO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CARMEN SOFIA</t>
+          <t>ROITH DERECK</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>17/06/2021</t>
+          <t>18/08/2020</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/08/2025</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,22 +6786,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>92069304</t>
+          <t>61036965</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MASHACURI</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AYLHYN RAYSA</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6810,16 +6810,16 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>19/10/2020</t>
+          <t>21/04/2007</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,27 +6849,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>81952159</t>
+          <t>92101549</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MENESES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ROITH DERECK</t>
+          <t>DANNA KENSLY IDA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>18/08/2020</t>
+          <t>14/07/2020</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>18/08/2025</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>61036965</t>
+          <t>81952194</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MENESES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ESPINAL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>KEYLA ALESSA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>21/04/2007</t>
+          <t>11/10/2020</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>92101549</t>
+          <t>22476772</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>MERCEDES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DANNA KENSLY IDA</t>
+          <t>MARIA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>14/07/2020</t>
+          <t>05/06/1971</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,27 +7038,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>81952194</t>
+          <t>92005854</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MENESES</t>
+          <t>MORI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>BANEO</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>KEYLA ALESSA</t>
+          <t>EDSON</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>11/10/2020</t>
+          <t>28/08/2020</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>28/08/2025</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,45 +7101,45 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>22476772</t>
+          <t>93693172</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MERCEDES</t>
+          <t>MUCHA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>MARIA</t>
+          <t>DYLAN ZAID JOSE</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>05/06/1971</t>
+          <t>21/01/2024</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>29/01/2024</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,35 +7164,35 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>92005854</t>
+          <t>92420729</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MORI</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BANEO</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EDSON</t>
+          <t>ADISSON LUNA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>28/08/2020</t>
+          <t>25/06/2021</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,35 +7227,35 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>93693172</t>
+          <t>92411951</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MUCHA</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>JERI</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DYLAN ZAID JOSE</t>
+          <t>DAHNA JHAIFEC</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>21/01/2024</t>
+          <t>20/06/2021</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>29/01/2024</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,45 +7290,45 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>92420729</t>
+          <t>61419547</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ADISSON LUNA</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>25/06/2021</t>
+          <t>04/09/2008</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>18/07/2013</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,7 +7353,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>92411951</t>
+          <t>62602011</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7363,35 +7363,35 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>JERI</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DAHNA JHAIFEC</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20/06/2021</t>
+          <t>26/04/2010</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>18/07/2013</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,7 +7416,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>61419547</t>
+          <t>81331653</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7431,30 +7431,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>WALTER</t>
+          <t>YESICA</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>04/09/2008</t>
+          <t>03/12/2014</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>18/07/2013</t>
+          <t>27/05/2016</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,22 +7479,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>62602011</t>
+          <t>91931802</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>ORDOÑEZ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>TAYPE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>JOSUE ANGEL</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>26/04/2010</t>
+          <t>15/07/2020</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>18/07/2013</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,45 +7542,45 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>81331653</t>
+          <t>93559063</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>BERROSPI</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>YESICA</t>
+          <t>DILAN DEREK</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>03/12/2014</t>
+          <t>28/09/2023</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>27/05/2016</t>
+          <t>29/09/2023</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,22 +7605,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>91931802</t>
+          <t>81907123</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ORDOÑEZ</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TAYPE</t>
+          <t>HUANACO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>JOSUE ANGEL</t>
+          <t>STEPHEN WILSON</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>15/07/2020</t>
+          <t>20/04/2020</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>20/04/2025</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,7 +7668,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>93559063</t>
+          <t>28282243</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BERROSPI</t>
+          <t>TIFONCIO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DILAN DEREK</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,21 +7692,21 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>28/09/2023</t>
+          <t>04/10/1971</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>29/09/2023</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,35 +7731,35 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>81907123</t>
+          <t>92320507</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HUANACO</t>
+          <t>GRANADOS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>STEPHEN WILSON</t>
+          <t>JISOO YAMILETH</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20/04/2020</t>
+          <t>18/04/2021</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>20/04/2025</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,45 +7794,45 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>28282243</t>
+          <t>94564900</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TIFONCIO</t>
+          <t>ACHA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>KEREN SARAI</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>04/10/1971</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,22 +7857,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>92320507</t>
+          <t>93480482</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GRANADOS</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>JISOO YAMILETH</t>
+          <t>ALEXANDRA SOFIA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7881,11 +7881,11 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>18/04/2021</t>
+          <t>27/07/2023</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>27/07/2023</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,22 +7920,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>94564900</t>
+          <t>92103095</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>PAITAN</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ACHA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>KEREN SARAI</t>
+          <t>JASMIN YAMILETH</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7944,11 +7944,11 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>09/11/2020</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>09/11/2025</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,35 +7983,35 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>93480482</t>
+          <t>81952166</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ALEXANDRA SOFIA</t>
+          <t>IKER ALEJANDRO</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>27/07/2023</t>
+          <t>30/01/2021</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>27/07/2023</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,45 +8046,45 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>94761959</t>
+          <t>62416726</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GUERREROS</t>
+          <t>JERI</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>MARIELYS ARISBETH</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>16/07/2007</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>05/10/2012</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,22 +8109,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>92103095</t>
+          <t>91362658</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PAITAN</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>JERI</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>JASMIN YAMILETH</t>
+          <t>KIMBERLY GIORGIA</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8133,11 +8133,11 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>09/11/2020</t>
+          <t>10/06/2019</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>09/11/2025</t>
+          <t>10/06/2024</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,45 +8172,45 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>81952166</t>
+          <t>60102393</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PARIAMANCCO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>IKER ALEJANDRO</t>
+          <t>LUZ SHEYLA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>30/01/2021</t>
+          <t>21/05/2005</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>23/12/2025</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,22 +8235,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>62416726</t>
+          <t>81952236</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>JERI</t>
+          <t>OROSCO</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>DYLAN GABRIEL</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8259,21 +8259,21 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>16/07/2007</t>
+          <t>13/08/2021</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>05/10/2012</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>91362658</t>
+          <t>81952216</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PILLACA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>JERI</t>
+          <t>INTIQUILLA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>KIMBERLY GIORGIA</t>
+          <t>ALEJANDRA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,11 +8322,11 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10/06/2019</t>
+          <t>27/05/2020</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>10/06/2024</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,22 +8361,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>60102393</t>
+          <t>91779056</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PARIAMANCCO</t>
+          <t>POLANCO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LUZ SHEYLA</t>
+          <t>HANNA KATALEYA</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8385,21 +8385,21 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>21/05/2005</t>
+          <t>17/03/2020</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>23/12/2025</t>
+          <t>17/03/2025</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,22 +8424,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>81952236</t>
+          <t>93537830</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>POZO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>OROSCO</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DYLAN GABRIEL</t>
+          <t>ALEXIS JHON</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8448,11 +8448,11 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>13/08/2021</t>
+          <t>23/03/2020</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>23/03/2025</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,27 +8487,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>81952216</t>
+          <t>92035969</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PILLACA</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>INTIQUILLA</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ALEJANDRA</t>
+          <t>DILAN GAEL</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>27/05/2020</t>
+          <t>27/09/2020</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>27/09/2025</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,22 +8550,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>91779056</t>
+          <t>92018669</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>POLANCO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>BAEZ</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>HANNA KATALEYA</t>
+          <t>ALISSON MIREYA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>17/03/2020</t>
+          <t>16/09/2020</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>17/03/2025</t>
+          <t>16/09/2025</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,27 +8613,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>93537830</t>
+          <t>81952156</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>POZO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>LAGO</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ALEXIS JHON</t>
+          <t>NAYSHA ISAMAR</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>23/03/2020</t>
+          <t>12/12/2020</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>23/03/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,22 +8676,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>92035969</t>
+          <t>81907106</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>DILAN GAEL</t>
+          <t>THOMAS ALBARO</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>27/09/2020</t>
+          <t>29/09/2020</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>27/09/2025</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>92018669</t>
+          <t>91736037</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BAEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ALISSON MIREYA</t>
+          <t>KAYRA CLEYDI</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>16/09/2020</t>
+          <t>19/02/2020</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>19/02/2025</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,35 +8802,35 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>81952156</t>
+          <t>94263521</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LAGO</t>
+          <t>CHIHUA</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NAYSHA ISAMAR</t>
+          <t>IKER JAZIEL</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>12/12/2020</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,35 +8865,35 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>81907106</t>
+          <t>92229552</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>THOMAS ALBARO</t>
+          <t>RUTH MISSHELL</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>29/09/2020</t>
+          <t>11/02/2021</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,35 +8928,35 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>91736037</t>
+          <t>92328541</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>KAYRA CLEYDI</t>
+          <t>EDRIC MAURICIO</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>19/02/2020</t>
+          <t>23/04/2021</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>19/02/2025</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,27 +8991,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>92497371</t>
+          <t>92409162</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>CHOCÑA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>TAITH VALENTINA</t>
+          <t>OSIEL EMILEC</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>17/08/2021</t>
+          <t>18/06/2021</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,22 +9054,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>94263521</t>
+          <t>81952223</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CHIHUA</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>IKER JAZIEL</t>
+          <t>LOLO</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9078,11 +9078,11 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>04/06/2021</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,22 +9117,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>92229552</t>
+          <t>94384573</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>RUTH MISSHELL</t>
+          <t>SULY</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9141,11 +9141,11 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>11/02/2021</t>
+          <t>13/09/2025</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,22 +9180,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>92328541</t>
+          <t>71054501</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>EDRIC MAURICIO</t>
+          <t>SEGUNDO GUILLERMO</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9204,21 +9204,21 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>23/04/2021</t>
+          <t>04/05/1997</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,22 +9243,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>92409162</t>
+          <t>92275464</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>REVOLLAR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CHOCÑA</t>
+          <t>CERAS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>OSIEL EMILEC</t>
+          <t>DAYMER WILSON</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>18/06/2021</t>
+          <t>17/03/2021</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9306,35 +9306,35 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>81952223</t>
+          <t>94742703</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>RIMAYCUNA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LOLO</t>
+          <t>BRENDA ARACELI</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>04/06/2021</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9369,22 +9369,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>94384573</t>
+          <t>91830656</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>ROCA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>RICRA</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SULY</t>
+          <t>LISBETH ANIELA</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9393,11 +9393,11 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>13/09/2025</t>
+          <t>27/04/2020</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>27/04/2025</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9432,45 +9432,45 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>71054501</t>
+          <t>92121034</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SEGUNDO GUILLERMO</t>
+          <t>BRIZETH ZAYURI</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>04/05/1997</t>
+          <t>21/11/2020</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9495,35 +9495,35 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>92275464</t>
+          <t>92175169</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>REVOLLAR</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CERAS</t>
+          <t>ZANABRIA</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DAYMER WILSON</t>
+          <t>FERIDE MERIDA KIKYO</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>17/03/2021</t>
+          <t>30/12/2020</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/12/2025</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9558,35 +9558,35 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>94742703</t>
+          <t>93546566</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>RIMAYCUNA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>BLACIDO</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>BRENDA ARACELI</t>
+          <t>OLIVER JAMES</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>21/09/2023</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9621,22 +9621,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>92480380</t>
+          <t>94203849</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>RISCO</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>FATMIR VICTORDANIEL</t>
+          <t>YAETH LIONEL</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9645,11 +9645,11 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>06/08/2021</t>
+          <t>07/04/2025</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9684,22 +9684,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>91830656</t>
+          <t>81952190</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ROCA</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LISBETH ANIELA</t>
+          <t>ALESSIA ABIGAIL</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>27/04/2020</t>
+          <t>15/03/2021</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>27/04/2025</t>
+          <t>15/03/2026</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9747,22 +9747,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>92121034</t>
+          <t>81952167</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>BRIZETH ZAYURI</t>
+          <t>ZALESKI YAZURI</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9771,11 +9771,11 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>21/11/2020</t>
+          <t>16/01/2021</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9810,22 +9810,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>92175169</t>
+          <t>81907141</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ZANABRIA</t>
+          <t>POMA</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>FERIDE MERIDA KIKYO</t>
+          <t>ANNA SARAI</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>30/12/2020</t>
+          <t>20/06/2020</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>30/12/2025</t>
+          <t>20/06/2025</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9873,45 +9873,45 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>93546566</t>
+          <t>44239287</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BLACIDO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>OLIVER JAMES</t>
+          <t>LIONESA</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>07/02/1986</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>21/09/2023</t>
+          <t>18/07/2013</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9936,22 +9936,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>94203849</t>
+          <t>91805861</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>YAETH LIONEL</t>
+          <t>STEVEN SNEYGER</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9960,31 +9960,31 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
+          <t>07/04/2020</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>1.NIÑO</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t>07/04/2025</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>09/04/2025</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9999,27 +9999,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>81952190</t>
+          <t>81952200</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>SHARETTE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ALESSIA ABIGAIL</t>
+          <t>AARON DARIEL JACK</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>15/03/2021</t>
+          <t>17/01/2021</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>17/01/2026</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10062,22 +10062,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>81952167</t>
+          <t>94314109</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>SHINTSIA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>CALLUPE</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ZALESKI YAZURI</t>
+          <t>AILANIA ZARIAH</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -10086,11 +10086,11 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>16/01/2021</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>16/08/2025</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10125,35 +10125,35 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>92522714</t>
+          <t>93473010</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>SHUMPATE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>ALMONACID</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>JASMIN ANTONELLA</t>
+          <t>LIAN JARET</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>04/09/2021</t>
+          <t>19/07/2023</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>29/07/2023</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10188,45 +10188,45 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>81907141</t>
+          <t>44449848</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>SHUMPATE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>POMA</t>
+          <t>CAYSAHUANA</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ANNA SARAI</t>
+          <t>EVER</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20/06/2020</t>
+          <t>23/10/1981</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>20/06/2025</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10251,35 +10251,35 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>92465800</t>
+          <t>91749480</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>SULCA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>GASTELU</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ANYELY CINDY LIZANDRA</t>
+          <t>DAYIRO JAIRO</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>26/07/2021</t>
+          <t>27/02/2020</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10314,45 +10314,45 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>44239287</t>
+          <t>81952212</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>TARAZONA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LIONESA</t>
+          <t>AXEL MARIANO</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>07/02/1986</t>
+          <t>03/10/2020</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>18/07/2013</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10377,27 +10377,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>91805861</t>
+          <t>91964630</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MARQUINA</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>STEVEN SNEYGER</t>
+          <t>BRITTANY ARACELY</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>07/04/2020</t>
+          <t>09/08/2020</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>07/04/2025</t>
+          <t>09/08/2025</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10440,22 +10440,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>81952200</t>
+          <t>43118682</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SHARETTE</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>AARON DARIEL JACK</t>
+          <t>FIDEL</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10464,21 +10464,21 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>17/01/2021</t>
+          <t>16/08/1983</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10503,22 +10503,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>94314109</t>
+          <t>92146515</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SHINTSIA</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CALLUPE</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>AILANIA ZARIAH</t>
+          <t>HEYDI NURIA</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10527,11 +10527,11 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>09/12/2020</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>16/08/2025</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10566,22 +10566,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>93473010</t>
+          <t>81952161</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SHUMPATE</t>
+          <t>TENORIO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ALMONACID</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LIAN JARET</t>
+          <t>JHON KEVIN</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10590,11 +10590,11 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>19/07/2023</t>
+          <t>14/06/2020</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>29/07/2023</t>
+          <t>14/06/2025</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10629,22 +10629,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>44449848</t>
+          <t>94245663</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SHUMPATE</t>
+          <t>TERRAZA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CAYSAHUANA</t>
+          <t>BARBARAN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>LIAM ALEXANDER</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10653,21 +10653,21 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>23/10/1981</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10692,22 +10692,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>91749480</t>
+          <t>81952173</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SULCA</t>
+          <t>TERRAZA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>GASTELU</t>
+          <t>CAÑAVI</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>DAYIRO JAIRO</t>
+          <t>DERECK ALEJANDRO</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>27/02/2020</t>
+          <t>11/09/2020</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10755,22 +10755,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>93107220</t>
+          <t>81907104</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TANANTA</t>
+          <t>TERRES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUINCHUNGA</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>YONSEO</t>
+          <t>HAIT DYLAN</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10779,11 +10779,11 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>07/09/2021</t>
+          <t>09/10/2020</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10818,35 +10818,35 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>81952212</t>
+          <t>92293798</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TARAZONA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>AXEL MARIANO</t>
+          <t>YAMELY MADAITH</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>03/10/2020</t>
+          <t>29/03/2021</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>29/03/2026</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10881,35 +10881,35 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>91964630</t>
+          <t>92228104</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MARQUINA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>BRITTANY ARACELY</t>
+          <t>JHONJAIRO ALEXIS</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>09/08/2020</t>
+          <t>10/02/2021</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>09/08/2025</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10944,22 +10944,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>43118682</t>
+          <t>81952195</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>TOSCANO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>FIDEL</t>
+          <t>GERALD ANDREWS</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10968,21 +10968,21 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>16/08/1983</t>
+          <t>16/07/2020</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -11007,35 +11007,35 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>92146515</t>
+          <t>92351412</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>UCHARIMA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>HEYDI NURIA</t>
+          <t>JESUS GAEL</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>09/12/2020</t>
+          <t>09/05/2021</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11070,22 +11070,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>81952161</t>
+          <t>49077400</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TENORIO</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t>CHORIHUANTE</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>JHON KEVIN</t>
+          <t>ROSSEL</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11094,21 +11094,21 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>14/06/2020</t>
+          <t>01/01/1989</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>14/06/2025</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11133,22 +11133,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>94245663</t>
+          <t>91868247</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TERRAZA</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BARBARAN</t>
+          <t>ACUÑA</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LIAM ALEXANDER</t>
+          <t>CARLOS ARJUNS</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -11157,11 +11157,11 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>26/05/2020</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11196,22 +11196,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>81952173</t>
+          <t>81952165</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TERRAZA</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CAÑAVI</t>
+          <t>CHUJUTALLI</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DERECK ALEJANDRO</t>
+          <t>JESUS ERIK JHON</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -11220,11 +11220,11 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>11/09/2020</t>
+          <t>14/01/2021</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11259,22 +11259,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>81907104</t>
+          <t>91733773</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TERRES</t>
+          <t>VENANCINO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>QUINCHUNGA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>HAIT DYLAN</t>
+          <t>AZIEL</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>09/10/2020</t>
+          <t>18/02/2020</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>18/02/2025</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11322,22 +11322,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>92293798</t>
+          <t>94674241</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VERA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>YAMUNAQUE</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>YAMELY MADAITH</t>
+          <t>ITZEL ANTONELLA</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11346,11 +11346,11 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>29/03/2021</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>29/03/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11385,22 +11385,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>92228104</t>
+          <t>92257077</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>JHONJAIRO ALEXIS</t>
+          <t>ROBERTH EFRAIN</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>10/02/2021</t>
+          <t>03/03/2021</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11448,35 +11448,35 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>81952195</t>
+          <t>92250111</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TOSCANO</t>
+          <t>VILLARRUEL</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CCANCCE</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>GERALD ANDREWS</t>
+          <t>YISEL ANGELA</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>16/07/2020</t>
+          <t>27/02/2021</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>16/07/2025</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11511,22 +11511,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>92351412</t>
+          <t>81952191</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>UCHARIMA</t>
+          <t>YACHA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>LLANTOY</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>JESUS GAEL</t>
+          <t>NAIN BEZAEEL</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>09/05/2021</t>
+          <t>04/03/2021</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11574,22 +11574,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>49077400</t>
+          <t>81952179</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>YANGARI</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CHORIHUANTE</t>
+          <t>NOLBERTO</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ROSSEL</t>
+          <t>ALDAIR JHUSUA</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11598,16 +11598,16 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>01/01/1989</t>
+          <t>04/10/2020</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11637,22 +11637,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>91868247</t>
+          <t>92402917</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>YAURI</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ACUÑA</t>
+          <t>MACHAO</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>CARLOS ARJUNS</t>
+          <t>MATTHEW HARMAN</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11661,11 +11661,11 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>26/05/2020</t>
+          <t>14/06/2021</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11700,35 +11700,35 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>81952165</t>
+          <t>81907124</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>YULGO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>CHUJUTALLI</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>JESUS ERIK JHON</t>
+          <t>NAOMI ADALIS</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>14/01/2021</t>
+          <t>21/06/2020</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11763,22 +11763,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>91733773</t>
+          <t>81780145</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>VENANCINO</t>
+          <t>ÑACO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>GOMES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>AZIEL</t>
+          <t>ELMER</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>18/02/2020</t>
+          <t>17/05/2020</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>18/02/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11826,35 +11826,35 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>94674241</t>
+          <t>81907139</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>VERA</t>
+          <t>ÑAÑA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>YAMUNAQUE</t>
+          <t>CHIMAYCO</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ITZEL ANTONELLA</t>
+          <t>LIAN</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/07/2020</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>09/07/2025</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11883,510 +11883,6 @@
         </is>
       </c>
       <c r="M182" t="n">
-        <v>120609</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>92257077</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>VILLANUEVA</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>HUAMANI</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>ROBERTH EFRAIN</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F183" t="n">
-        <v>5</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>03/03/2021</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>03/03/2026</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>VIZCATAN DEL ENE</t>
-        </is>
-      </c>
-      <c r="M183" t="n">
-        <v>120609</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>92250111</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>VILLARRUEL</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>CCANCCE</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>YISEL ANGELA</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F184" t="n">
-        <v>5</v>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>27/02/2021</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>27/02/2026</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>VIZCATAN DEL ENE</t>
-        </is>
-      </c>
-      <c r="M184" t="n">
-        <v>120609</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>81952191</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>YACHA</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>LLANTOY</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>NAIN BEZAEEL</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F185" t="n">
-        <v>5</v>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>04/03/2021</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>VIZCATAN DEL ENE</t>
-        </is>
-      </c>
-      <c r="M185" t="n">
-        <v>120609</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>81952179</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>YANGARI</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>NOLBERTO</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>ALDAIR JHUSUA</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F186" t="n">
-        <v>6</v>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>04/10/2020</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>27/10/2025</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>VIZCATAN DEL ENE</t>
-        </is>
-      </c>
-      <c r="M186" t="n">
-        <v>120609</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>92402917</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>YAURI</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>MACHAO</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>MATTHEW HARMAN</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F187" t="n">
-        <v>5</v>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>14/06/2021</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>VIZCATAN DEL ENE</t>
-        </is>
-      </c>
-      <c r="M187" t="n">
-        <v>120609</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>81907124</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>YULGO</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>GUZMAN</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>NAOMI ADALIS</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="F188" t="n">
-        <v>6</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>21/06/2020</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>30/07/2025</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>VIZCATAN DEL ENE</t>
-        </is>
-      </c>
-      <c r="M188" t="n">
-        <v>120609</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>81780145</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>ÑACO</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>GOMES</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>ELMER</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F189" t="n">
-        <v>6</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>17/05/2020</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>27/05/2025</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>VIZCATAN DEL ENE</t>
-        </is>
-      </c>
-      <c r="M189" t="n">
-        <v>120609</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>81907139</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>ÑAÑA</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>CHIMAYCO</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>LIAN</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F190" t="n">
-        <v>6</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>09/07/2020</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>1.NIÑO</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>09/07/2025</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>VIZCATAN DEL ENE</t>
-        </is>
-      </c>
-      <c r="M190" t="n">
         <v>120609</v>
       </c>
     </row>
